--- a/IMS/src/main/webapp/excelTemplate/inspectionDetail.xlsx
+++ b/IMS/src/main/webapp/excelTemplate/inspectionDetail.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\h1\excelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\innost\Desktop\IMS수정txt\excelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16950" windowHeight="12060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,10 +40,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>점검관리 상세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 점검구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,26 +80,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>필드1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>필드5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>점검일자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>첨부 파일명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 점검자 소속</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,10 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 작성일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>${info.eRegistrant}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,83 +124,115 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>${info.eRemark}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${file.eFileName }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;/jx:forEach&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;jx:forEach var="file" items="${file}" &gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;jx:forEach var="asset" items="${asset}" &gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eAssetName }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eAssetMaker }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eAssetModel }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eAssetType }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eNetworkType }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eDeviceType }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eField3 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eField4 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eField5 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eItemRemark }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eItemOther }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eItemInspectionDate }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eField1 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${asset.eField2 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>${info.eInspectorOrg}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>${info.eRemark}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${file.eFileName }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;/jx:forEach&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;jx:forEach var="file" items="${file}" &gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;jx:forEach var="asset" items="${asset}" &gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eAssetName }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eAssetMaker }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eAssetModel }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eAssetType }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eNetworkType }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eDeviceType }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eField3 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eField4 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eField5 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eItemRemark }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eItemOther }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eItemInspectionDate }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eField1 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${asset.eField2 }</t>
+    <t>${info.eField1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${info.eField2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${info.eField3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${info.eField4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${info.eField5}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 등록일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점검정보 상세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점검 서류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1415,7 +1415,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="174.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="B3" s="5"/>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="34" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
@@ -1477,11 +1477,11 @@
       <c r="G5" s="34"/>
       <c r="H5" s="35"/>
       <c r="I5" s="36" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="J5" s="37"/>
       <c r="K5" s="34" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L5" s="34"/>
       <c r="M5" s="34"/>
@@ -1491,11 +1491,11 @@
     </row>
     <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="46"/>
       <c r="C6" s="42" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
@@ -1503,11 +1503,11 @@
       <c r="G6" s="32"/>
       <c r="H6" s="33"/>
       <c r="I6" s="38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" s="39"/>
       <c r="K6" s="32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L6" s="32"/>
       <c r="M6" s="32"/>
@@ -1517,11 +1517,11 @@
     </row>
     <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="42" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
@@ -1539,11 +1539,11 @@
     </row>
     <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="46"/>
       <c r="C8" s="43" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
@@ -1551,11 +1551,11 @@
       <c r="G8" s="30"/>
       <c r="H8" s="31"/>
       <c r="I8" s="40" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J8" s="41"/>
       <c r="K8" s="30" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
@@ -1565,11 +1565,11 @@
     </row>
     <row r="9" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="46"/>
       <c r="C9" s="27" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="28"/>
@@ -1588,7 +1588,7 @@
     <row r="10" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="6"/>
     </row>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="13" spans="1:16" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="44" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B13" s="47"/>
       <c r="C13" s="47"/>
@@ -1633,7 +1633,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -1653,7 +1653,7 @@
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
       <c r="H15" s="19" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
@@ -1673,7 +1673,7 @@
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
       <c r="H16" s="19" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
@@ -1712,46 +1712,46 @@
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>14</v>
-      </c>
       <c r="H20" s="11" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="K20" s="45"/>
       <c r="L20" s="11" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="7" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B21" s="23"/>
       <c r="C21" s="22"/>
@@ -1771,53 +1771,53 @@
     </row>
     <row r="22" spans="1:16" s="7" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C22" s="22"/>
       <c r="D22" s="13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="J22" s="23" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K22" s="22"/>
       <c r="L22" s="13" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="7" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="22"/>
